--- a/public/samples/remains/ccdc.xlsx
+++ b/public/samples/remains/ccdc.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/Kho còn lại/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{837BE021-26EB-1E41-8D9E-682AD0FA541C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{B59CD8F2-FE1A-784E-A689-F7B5968830BD}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="356">
   <si>
     <t>Tồn</t>
   </si>
@@ -55,6 +44,9 @@
   </si>
   <si>
     <t>SL - Cái</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>CD0001</t>
@@ -1095,29 +1087,370 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1125,27 +1458,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1194,7 +1813,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1227,26 +1846,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1279,23 +1881,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1437,27 +2022,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0C9DA5-850F-B34F-84B8-1292B3EF2542}">
-  <dimension ref="A1:I159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J159"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="8:9">
       <c r="H1" s="2"/>
       <c r="I1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1485,115 +2065,118 @@
       <c r="I2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2">
         <v>44927</v>
@@ -1602,27 +2185,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2">
         <v>44927</v>
@@ -1631,27 +2214,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2">
         <v>44927</v>
@@ -1660,27 +2243,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2">
         <v>44927</v>
@@ -1689,27 +2272,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2">
         <v>44927</v>
@@ -1718,27 +2301,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2">
         <v>44927</v>
@@ -1747,27 +2330,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="2">
         <v>44927</v>
@@ -1776,27 +2359,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="2">
         <v>44927</v>
@@ -1805,27 +2388,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2">
         <v>44927</v>
@@ -1834,172 +2417,172 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2">
         <v>44927</v>
@@ -2008,56 +2591,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="C21" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2">
         <v>44927</v>
@@ -2066,27 +2649,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
         <v>59</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="2">
         <v>44927</v>
@@ -2095,27 +2678,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2">
         <v>44927</v>
@@ -2124,27 +2707,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
         <v>64</v>
-      </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="2">
         <v>44927</v>
@@ -2153,27 +2736,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26">
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2">
         <v>44927</v>
@@ -2182,27 +2765,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="2">
         <v>44927</v>
@@ -2211,27 +2794,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="2">
         <v>44927</v>
@@ -2240,27 +2823,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" s="2">
         <v>44927</v>
@@ -2269,27 +2852,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" s="2">
         <v>44927</v>
@@ -2298,27 +2881,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
         <v>80</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" t="s">
-        <v>79</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" s="2">
         <v>44927</v>
@@ -2327,27 +2910,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32">
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" s="2">
         <v>44927</v>
@@ -2356,27 +2939,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" s="2">
         <v>44927</v>
@@ -2385,27 +2968,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>89</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" s="2">
         <v>44927</v>
@@ -2414,27 +2997,27 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
         <v>90</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" t="s">
-        <v>89</v>
       </c>
       <c r="E35">
         <v>100</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" s="2">
         <v>44927</v>
@@ -2443,27 +3026,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>94</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E36">
         <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="2">
         <v>44927</v>
@@ -2472,27 +3055,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>54</v>
+        <v>97</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H37" s="2">
         <v>44927</v>
@@ -2501,27 +3084,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H38" s="2">
         <v>44927</v>
@@ -2530,27 +3113,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>54</v>
+        <v>101</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H39" s="2">
         <v>44927</v>
@@ -2559,27 +3142,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>54</v>
+        <v>103</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E40">
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" s="2">
         <v>44927</v>
@@ -2588,27 +3171,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>54</v>
+        <v>105</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E41">
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H41" s="2">
         <v>44927</v>
@@ -2617,27 +3200,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42">
         <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H42" s="2">
         <v>44927</v>
@@ -2646,27 +3229,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" s="2">
         <v>44927</v>
@@ -2675,27 +3258,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>54</v>
+        <v>111</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" s="2">
         <v>44927</v>
@@ -2704,27 +3287,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>54</v>
+        <v>113</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H45" s="2">
         <v>44927</v>
@@ -2733,27 +3316,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>54</v>
+        <v>115</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" s="2">
         <v>44927</v>
@@ -2762,27 +3345,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>54</v>
+        <v>117</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" s="2">
         <v>44927</v>
@@ -2791,27 +3374,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>54</v>
+        <v>119</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H48" s="2">
         <v>44927</v>
@@ -2820,27 +3403,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>54</v>
+        <v>121</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H49" s="2">
         <v>44927</v>
@@ -2849,27 +3432,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>54</v>
+        <v>123</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E50">
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H50" s="2">
         <v>44927</v>
@@ -2878,27 +3461,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>54</v>
+        <v>125</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" s="2">
         <v>44927</v>
@@ -2907,27 +3490,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>54</v>
+        <v>128</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H52" s="2">
         <v>44927</v>
@@ -2936,27 +3519,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>54</v>
+        <v>130</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H53" s="2">
         <v>44927</v>
@@ -2965,27 +3548,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E54">
         <v>5</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H54" s="2">
         <v>44927</v>
@@ -2994,27 +3577,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>54</v>
+        <v>134</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E55">
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H55" s="2">
         <v>44927</v>
@@ -3023,27 +3606,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>54</v>
+        <v>137</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E56">
         <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H56" s="2">
         <v>44927</v>
@@ -3052,27 +3635,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B57" t="s">
-        <v>138</v>
-      </c>
-      <c r="C57" s="3" t="s">
         <v>139</v>
       </c>
+      <c r="C57" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H57" s="2">
         <v>44927</v>
@@ -3081,27 +3664,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B58" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H58" s="2">
         <v>44927</v>
@@ -3110,27 +3693,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E59">
         <v>2</v>
       </c>
       <c r="F59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H59" s="2">
         <v>44927</v>
@@ -3139,27 +3722,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H60" s="2">
         <v>44927</v>
@@ -3168,27 +3751,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H61" s="2">
         <v>44927</v>
@@ -3197,27 +3780,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H62" s="2">
         <v>44927</v>
@@ -3226,27 +3809,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E63">
         <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H63" s="2">
         <v>44927</v>
@@ -3255,27 +3838,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H64" s="2">
         <v>44927</v>
@@ -3284,27 +3867,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H65" s="2">
         <v>44927</v>
@@ -3313,27 +3896,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H66" s="2">
         <v>44927</v>
@@ -3342,27 +3925,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>139</v>
+        <v>160</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E67">
         <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H67" s="2">
         <v>44927</v>
@@ -3371,27 +3954,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>139</v>
+        <v>163</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E68">
         <v>100</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H68" s="2">
         <v>44927</v>
@@ -3400,27 +3983,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>139</v>
+        <v>165</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H69" s="2">
         <v>44927</v>
@@ -3429,27 +4012,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>139</v>
+        <v>167</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H70" s="2">
         <v>44927</v>
@@ -3458,27 +4041,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>139</v>
+        <v>169</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E71">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H71" s="2">
         <v>44927</v>
@@ -3487,27 +4070,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>139</v>
+        <v>171</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H72" s="2">
         <v>44927</v>
@@ -3516,27 +4099,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
-      </c>
-      <c r="C73" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="C73" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="D73" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E73">
         <v>6</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H73" s="2">
         <v>44927</v>
@@ -3545,27 +4128,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
+        <v>175</v>
+      </c>
+      <c r="B74" t="s">
+        <v>176</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B74" t="s">
-        <v>175</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H74" s="2">
         <v>44927</v>
@@ -3574,27 +4157,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>178</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H75" s="2">
         <v>44927</v>
@@ -3603,27 +4186,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E76">
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H76" s="2">
         <v>44927</v>
@@ -3632,27 +4215,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B77" t="s">
-        <v>183</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D77" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E77">
         <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H77" s="2">
         <v>44927</v>
@@ -3661,27 +4244,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>173</v>
+        <v>186</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D78" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E78">
         <v>2</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H78" s="2">
         <v>44927</v>
@@ -3690,27 +4273,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>173</v>
+        <v>188</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E79">
         <v>2</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H79" s="2">
         <v>44927</v>
@@ -3719,27 +4302,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B80" t="s">
-        <v>189</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H80" s="2">
         <v>44927</v>
@@ -3748,27 +4331,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B81" t="s">
-        <v>191</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>173</v>
+        <v>192</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H81" s="2">
         <v>44927</v>
@@ -3777,27 +4360,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>173</v>
+        <v>194</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H82" s="2">
         <v>44927</v>
@@ -3806,27 +4389,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B83" t="s">
-        <v>195</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>173</v>
+        <v>196</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H83" s="2">
         <v>44927</v>
@@ -3835,27 +4418,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B84" t="s">
-        <v>197</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>173</v>
+        <v>198</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H84" s="2">
         <v>44927</v>
@@ -3864,27 +4447,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B85" t="s">
-        <v>199</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>173</v>
+        <v>200</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H85" s="2">
         <v>44927</v>
@@ -3893,27 +4476,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>201</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D86" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E86">
         <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H86" s="2">
         <v>44927</v>
@@ -3922,27 +4505,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B87" t="s">
-        <v>203</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>173</v>
+        <v>204</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E87">
         <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H87" s="2">
         <v>44927</v>
@@ -3951,27 +4534,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>173</v>
+        <v>206</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H88" s="2">
         <v>44927</v>
@@ -3980,27 +4563,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>207</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>173</v>
+        <v>208</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H89" s="2">
         <v>44927</v>
@@ -4009,27 +4592,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>209</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>173</v>
+        <v>210</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H90" s="2">
         <v>44927</v>
@@ -4038,27 +4621,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B91" t="s">
-        <v>211</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>173</v>
+        <v>212</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E91">
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H91" s="2">
         <v>44927</v>
@@ -4067,27 +4650,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B92" t="s">
-        <v>213</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>173</v>
+        <v>214</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H92" s="2">
         <v>44927</v>
@@ -4096,27 +4679,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B93" t="s">
-        <v>143</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>173</v>
+        <v>144</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H93" s="2">
         <v>44927</v>
@@ -4125,27 +4708,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B94" t="s">
-        <v>216</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>173</v>
+        <v>217</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E94">
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H94" s="2">
         <v>44927</v>
@@ -4154,27 +4737,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B95" t="s">
-        <v>218</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>173</v>
+        <v>219</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E95">
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H95" s="2">
         <v>44927</v>
@@ -4183,27 +4766,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B96" t="s">
-        <v>153</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>173</v>
+        <v>154</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H96" s="2">
         <v>44927</v>
@@ -4212,27 +4795,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>173</v>
+        <v>222</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E97">
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H97" s="2">
         <v>44927</v>
@@ -4241,27 +4824,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B98" t="s">
-        <v>223</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>173</v>
+        <v>224</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E98">
         <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H98" s="2">
         <v>44927</v>
@@ -4270,27 +4853,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>173</v>
+        <v>226</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E99">
         <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H99" s="2">
         <v>44927</v>
@@ -4299,27 +4882,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>173</v>
+        <v>50</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D100" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H100" s="2">
         <v>44927</v>
@@ -4328,27 +4911,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>173</v>
+        <v>229</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D101" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E101">
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H101" s="2">
         <v>44927</v>
@@ -4357,27 +4940,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H102" s="2">
         <v>44927</v>
@@ -4386,27 +4969,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B103" t="s">
-        <v>231</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>173</v>
+        <v>232</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H103" s="2">
         <v>44927</v>
@@ -4415,27 +4998,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B104" t="s">
-        <v>233</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>173</v>
+        <v>234</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H104" s="2">
         <v>44927</v>
@@ -4444,27 +5027,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B105" t="s">
-        <v>235</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>173</v>
+        <v>236</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D105" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H105" s="2">
         <v>44927</v>
@@ -4473,27 +5056,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B106" t="s">
-        <v>237</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>173</v>
+        <v>238</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E106">
         <v>10</v>
       </c>
       <c r="F106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H106" s="2">
         <v>44927</v>
@@ -4502,27 +5085,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B107" t="s">
-        <v>240</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>173</v>
+        <v>241</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E107">
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H107" s="2">
         <v>44927</v>
@@ -4531,85 +5114,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s">
-        <v>242</v>
-      </c>
-      <c r="C108" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="C108" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="D108" t="s">
+        <v>245</v>
+      </c>
+      <c r="E108">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I108">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>246</v>
+      </c>
+      <c r="B109" t="s">
+        <v>247</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E108">
-        <v>15</v>
-      </c>
-      <c r="F108" t="s">
-        <v>14</v>
-      </c>
-      <c r="G108" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I108">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="D109" t="s">
         <v>245</v>
       </c>
-      <c r="B109" t="s">
-        <v>246</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="E109">
+        <v>15</v>
+      </c>
+      <c r="F109" t="s">
+        <v>15</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I109">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E109">
-        <v>15</v>
-      </c>
-      <c r="F109" t="s">
-        <v>14</v>
-      </c>
-      <c r="G109" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I109">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>247</v>
-      </c>
-      <c r="B110" t="s">
-        <v>248</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="D110" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E110">
         <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H110" s="2">
         <v>44927</v>
@@ -4618,27 +5201,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B111" t="s">
-        <v>250</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D111" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E111">
         <v>1.5</v>
       </c>
       <c r="F111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H111" s="2">
         <v>44927</v>
@@ -4647,27 +5230,27 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B112" t="s">
-        <v>253</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D112" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E112">
         <v>30</v>
       </c>
       <c r="F112" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H112" s="2">
         <v>44927</v>
@@ -4676,27 +5259,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
+        <v>257</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D113" t="s">
         <v>255</v>
-      </c>
-      <c r="B113" t="s">
-        <v>256</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D113" t="s">
-        <v>254</v>
       </c>
       <c r="E113">
         <v>30</v>
       </c>
       <c r="F113" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H113" s="2">
         <v>44927</v>
@@ -4705,27 +5288,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>243</v>
+        <v>259</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D114" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E114">
         <v>30</v>
       </c>
       <c r="F114" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H114" s="2">
         <v>44927</v>
@@ -4734,27 +5317,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B115" t="s">
-        <v>260</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D115" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E115">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H115" s="2">
         <v>44927</v>
@@ -4763,27 +5346,27 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
+        <v>263</v>
+      </c>
+      <c r="B116" t="s">
+        <v>264</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D116" t="s">
         <v>262</v>
-      </c>
-      <c r="B116" t="s">
-        <v>263</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D116" t="s">
-        <v>261</v>
       </c>
       <c r="E116">
         <v>40</v>
       </c>
       <c r="F116" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H116" s="2">
         <v>44927</v>
@@ -4792,27 +5375,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E117">
         <v>35</v>
       </c>
       <c r="F117" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H117" s="2">
         <v>44927</v>
@@ -4821,27 +5404,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C118" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D118" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E118">
         <v>20</v>
       </c>
       <c r="F118" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H118" s="2">
         <v>44927</v>
@@ -4850,27 +5433,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B119" t="s">
-        <v>269</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>243</v>
+        <v>270</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D119" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E119">
         <v>20</v>
       </c>
       <c r="F119" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H119" s="2">
         <v>44927</v>
@@ -4879,27 +5462,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B120" t="s">
-        <v>271</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>243</v>
+        <v>272</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E120">
         <v>20</v>
       </c>
       <c r="F120" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H120" s="2">
         <v>44927</v>
@@ -4908,27 +5491,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B121" t="s">
-        <v>273</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>243</v>
+        <v>274</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E121">
         <v>4</v>
       </c>
       <c r="F121" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G121" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H121" s="2">
         <v>44927</v>
@@ -4937,27 +5520,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B122" t="s">
-        <v>275</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>243</v>
+        <v>276</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E122">
         <v>2</v>
       </c>
       <c r="F122" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H122" s="2">
         <v>44927</v>
@@ -4966,27 +5549,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>243</v>
+        <v>278</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D123" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E123">
         <v>0.5</v>
       </c>
       <c r="F123" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H123" s="2">
         <v>44927</v>
@@ -4995,27 +5578,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>243</v>
+        <v>280</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D124" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E124">
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H124" s="2">
         <v>44927</v>
@@ -5024,27 +5607,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>243</v>
+        <v>282</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E125">
         <v>5</v>
       </c>
       <c r="F125" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H125" s="2">
         <v>44927</v>
@@ -5053,27 +5636,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>243</v>
+        <v>37</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D126" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E126">
         <v>2</v>
       </c>
       <c r="F126" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H126" s="2">
         <v>44927</v>
@@ -5082,27 +5665,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B127" t="s">
-        <v>284</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>243</v>
+        <v>285</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D127" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E127">
         <v>0.5</v>
       </c>
       <c r="F127" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H127" s="2">
         <v>44927</v>
@@ -5111,27 +5694,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B128" t="s">
-        <v>286</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>243</v>
+        <v>287</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D128" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E128">
         <v>5</v>
       </c>
       <c r="F128" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G128" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H128" s="2">
         <v>44927</v>
@@ -5140,27 +5723,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B129" t="s">
-        <v>288</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>243</v>
+        <v>289</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D129" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H129" s="2">
         <v>44927</v>
@@ -5169,27 +5752,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B130" t="s">
-        <v>290</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>243</v>
+        <v>291</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D130" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E130">
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H130" s="2">
         <v>44927</v>
@@ -5198,27 +5781,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B131" t="s">
-        <v>292</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>243</v>
+        <v>293</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H131" s="2">
         <v>44927</v>
@@ -5227,27 +5810,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B132" t="s">
-        <v>294</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>243</v>
+        <v>295</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E132">
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H132" s="2">
         <v>44927</v>
@@ -5256,27 +5839,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B133" t="s">
-        <v>296</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>243</v>
+        <v>297</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D133" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E133">
         <v>10</v>
       </c>
       <c r="F133" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H133" s="2">
         <v>44927</v>
@@ -5285,27 +5868,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" t="s">
+        <v>300</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D134" t="s">
         <v>298</v>
-      </c>
-      <c r="B134" t="s">
-        <v>299</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D134" t="s">
-        <v>297</v>
       </c>
       <c r="E134">
         <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H134" s="2">
         <v>44927</v>
@@ -5314,27 +5897,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" t="s">
         <v>300</v>
       </c>
-      <c r="B135" t="s">
-        <v>299</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>243</v>
+      <c r="C135" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D135" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E135">
         <v>10</v>
       </c>
       <c r="F135" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H135" s="2">
         <v>44927</v>
@@ -5343,27 +5926,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B136" t="s">
-        <v>302</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>243</v>
+        <v>303</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D136" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E136">
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H136" s="2">
         <v>44927</v>
@@ -5372,27 +5955,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B137" t="s">
-        <v>304</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>243</v>
+        <v>305</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D137" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E137">
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G137" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H137" s="2">
         <v>44927</v>
@@ -5401,27 +5984,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B138" t="s">
-        <v>306</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>243</v>
+        <v>307</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D138" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E138">
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G138" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H138" s="2">
         <v>44927</v>
@@ -5430,27 +6013,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B139" t="s">
-        <v>308</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>243</v>
+        <v>309</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D139" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E139">
         <v>100</v>
       </c>
       <c r="F139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G139" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H139" s="2">
         <v>44927</v>
@@ -5459,27 +6042,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B140" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>243</v>
+        <v>311</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E140">
         <v>40</v>
       </c>
       <c r="F140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G140" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H140" s="2">
         <v>44927</v>
@@ -5488,27 +6071,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B141" t="s">
-        <v>312</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>243</v>
+        <v>313</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D141" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E141">
         <v>5</v>
       </c>
       <c r="F141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H141" s="2">
         <v>44927</v>
@@ -5517,27 +6100,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" t="s">
-        <v>314</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>243</v>
+        <v>315</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D142" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E142">
         <v>5</v>
       </c>
       <c r="F142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H142" s="2">
         <v>44927</v>
@@ -5546,27 +6129,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B143" t="s">
-        <v>316</v>
-      </c>
-      <c r="C143" s="1" t="s">
         <v>317</v>
       </c>
+      <c r="C143" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="D143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E143">
         <v>8</v>
       </c>
       <c r="F143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H143" s="2">
         <v>44927</v>
@@ -5575,27 +6158,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" t="s">
+        <v>320</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B144" t="s">
-        <v>319</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="D144" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G144" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H144" s="2">
         <v>44927</v>
@@ -5604,27 +6187,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B145" t="s">
-        <v>321</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="D145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E145">
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G145" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H145" s="2">
         <v>44927</v>
@@ -5633,27 +6216,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B146" t="s">
-        <v>323</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="D146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H146" s="2">
         <v>44927</v>
@@ -5662,27 +6245,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B147" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="D147" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E147">
         <v>5</v>
       </c>
       <c r="F147" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G147" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H147" s="2">
         <v>44927</v>
@@ -5691,27 +6274,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B148" t="s">
-        <v>328</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="D148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E148">
         <v>10</v>
       </c>
       <c r="F148" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H148" s="2">
         <v>44927</v>
@@ -5720,85 +6303,85 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" t="s">
+        <v>332</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D149" t="s">
+        <v>177</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" t="s">
+        <v>334</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D150" t="s">
+        <v>177</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" t="s">
+        <v>336</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D151" t="s">
         <v>330</v>
-      </c>
-      <c r="B149" t="s">
-        <v>331</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D149" t="s">
-        <v>176</v>
-      </c>
-      <c r="E149">
-        <v>2</v>
-      </c>
-      <c r="F149" t="s">
-        <v>14</v>
-      </c>
-      <c r="G149" t="s">
-        <v>15</v>
-      </c>
-      <c r="H149" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>332</v>
-      </c>
-      <c r="B150" t="s">
-        <v>333</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D150" t="s">
-        <v>176</v>
-      </c>
-      <c r="E150">
-        <v>2</v>
-      </c>
-      <c r="F150" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I150">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>334</v>
-      </c>
-      <c r="B151" t="s">
-        <v>335</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D151" t="s">
-        <v>329</v>
       </c>
       <c r="E151">
         <v>6</v>
       </c>
       <c r="F151" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H151" s="2">
         <v>44927</v>
@@ -5807,27 +6390,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B152" t="s">
-        <v>337</v>
-      </c>
-      <c r="C152" s="1" t="s">
         <v>338</v>
       </c>
+      <c r="C152" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="D152" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E152">
         <v>5</v>
       </c>
       <c r="F152" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G152" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H152" s="2">
         <v>44927</v>
@@ -5836,27 +6419,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" t="s">
+        <v>342</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D153" t="s">
         <v>340</v>
-      </c>
-      <c r="B153" t="s">
-        <v>341</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D153" t="s">
-        <v>339</v>
       </c>
       <c r="E153">
         <v>30</v>
       </c>
       <c r="F153" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G153" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H153" s="2">
         <v>44927</v>
@@ -5865,56 +6448,56 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B154" t="s">
-        <v>343</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="D154" t="s">
+        <v>340</v>
+      </c>
+      <c r="E154">
+        <v>15</v>
+      </c>
+      <c r="F154" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" t="s">
+        <v>16</v>
+      </c>
+      <c r="H154" s="2">
+        <v>44927</v>
+      </c>
+      <c r="I154">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>345</v>
+      </c>
+      <c r="B155" t="s">
+        <v>346</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E154">
-        <v>15</v>
-      </c>
-      <c r="F154" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" s="2">
-        <v>44927</v>
-      </c>
-      <c r="I154">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>344</v>
-      </c>
-      <c r="B155" t="s">
-        <v>345</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="D155" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E155">
         <v>10</v>
       </c>
       <c r="F155" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G155" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H155" s="2">
         <v>44927</v>
@@ -5923,27 +6506,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B156" t="s">
-        <v>347</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>338</v>
+        <v>348</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="D156" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E156">
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H156" s="2">
         <v>44927</v>
@@ -5952,27 +6535,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B157" t="s">
-        <v>349</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="D157" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E157">
         <v>30</v>
       </c>
       <c r="F157" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H157" s="2">
         <v>44927</v>
@@ -5981,27 +6564,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B158" t="s">
-        <v>352</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>338</v>
+        <v>353</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="D158" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E158">
         <v>20</v>
       </c>
       <c r="F158" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H158" s="2">
         <v>44927</v>
@@ -6010,27 +6593,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B159" t="s">
-        <v>354</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>338</v>
+        <v>355</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="D159" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E159">
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G159" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H159" s="2">
         <v>44927</v>
@@ -6041,5 +6624,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>